--- a/ОВК/291-ОВК.Р Расчёты.xlsx
+++ b/ОВК/291-ОВК.Р Расчёты.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>канальный</t>
+          <t>настенный</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>канальный</t>
+          <t>настенный</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный, Qх=7.1 кВт</t>
+          <t>Внутренний блок настенный, Qх=7.1 кВт</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный, Qх=5.6 кВт</t>
+          <t>Внутренний блок настенный, Qх=5.6 кВт</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
@@ -4350,23 +4350,19 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Дренажный насос (для канальных блоков)</t>
+          <t>Опора наружного блока (рама на фундаментных блоках)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>ВБ канальные</t>
-        </is>
-      </c>
+      <c r="F58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4376,41 +4372,19 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Опора наружного блока (рама на фундаментных блоках)</t>
+          <t>Пульт управления проводной индивидуальный</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Пульт управления проводной индивидуальный</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ОВК/291-ОВК.Р Расчёты.xlsx
+++ b/ОВК/291-ОВК.Р Расчёты.xlsx
@@ -3088,13 +3088,13 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная с сеткой 500×300</t>
+          <t>Узел воздухозаборный через фальцевую кровлю Ø315 с зонтом и сеткой</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Фронтон</t>
+          <t>Наружный воздух П1</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,11 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Выброс В1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3136,7 +3140,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный круглый (ДПУ-М) Ø125 / Ø160</t>
+          <t>Диффузор потолочный круглый (ДПУ-М) Ø100…Ø200</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2 этаж, по схемам</t>
+          <t>2 этаж, по плану</t>
         </is>
       </c>
     </row>
@@ -3172,11 +3176,11 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1 этаж, по схемам</t>
+          <t>1 этаж, по плану</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3192,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Распределительный коллектор (камера статического давления) Ø250/Ø160, 10 выходов Ø90, со звукопоглощением</t>
+          <t>Распределительный коллектор (камера статического давления) Ø200/Ø160, 6…14 выходов Ø90, со звукопоглощением и ревизией</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -3202,7 +3206,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>В вент. коробе</t>
+          <t>РК1–РК4: РК1=14, РК2=6, РК3=7, РК4=8 вых.</t>
         </is>
       </c>
     </row>
@@ -3224,11 +3228,11 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19+14 линий, ≈12 м</t>
+          <t>21+14 линий × ≈12 м</t>
         </is>
       </c>
     </row>

--- a/ОВК/291-ОВК.Р Расчёты.xlsx
+++ b/ОВК/291-ОВК.Р Расчёты.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Воздухообмен" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Системы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кондиционирование" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Увлажнение" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Электронагрузки ОВК" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кондиционирование" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,7 +745,7 @@
         <v/>
       </c>
       <c r="G6" s="2" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -768,7 +770,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3 крат + воздух на горение (уточнить по типу котла)</t>
+          <t>Вытяжка 3 крат; приток = вытяжка + воздух на горение пеллетного котла 30 кВт ≈ 60 м³/ч (уточнить по паспорту котла)</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1066,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Просушка 6 крат (h=2,4 м); приток перетоком из зоны отдыха</t>
+          <t>Просушка 6 крат (h=2,4 м); приток перетоком из зоны отдыха; режим — по гигростату</t>
         </is>
       </c>
     </row>
@@ -2129,13 +2131,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
     </row>
@@ -2157,7 +2159,7 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>η рекуператора=0.75; t после рекуп.=10.2 °C; Q=0,336·L·Δt=3.44 кВт</t>
+          <t>η рекуператора=0.8; t после рекуп.=12.6 °C; Q=0,336·L·Δt=2.61 кВт; принят водяной калорифер 7 кВт (запас на оттайку/обход ротора)</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2174,7 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>от -25 до +16 °C; Q=5.51 кВт</t>
+          <t>от -25 до +16 °C; Q=5.51 кВт; водяной калорифер 5.5 кВт</t>
         </is>
       </c>
     </row>
@@ -2182,6 +2184,442 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>L притока, м³/ч</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Δx, г/кг</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>G расч, кг/ч</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ПУ, кг/ч</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>N, кВт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ПУ1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Детская 10</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E2" s="2">
+        <f>C2*1.2*D2/1000</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ПУ2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Детская 12</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E3" s="2">
+        <f>C3*1.2*D3/1000</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ПУ3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Детская 14</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E4" s="2">
+        <f>C4*1.2*D4/1000</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ПУ4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Гостевая 7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E5" s="2">
+        <f>C5*1.2*D5/1000</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ПУ5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Мастер-спальня 3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E6" s="2">
+        <f>C6*1.2*D6/1000</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ПУ6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Гостиная и кухня-столовая (через ВК-1)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E7" s="2">
+        <f>C7*1.2*D7/1000</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="2">
+        <f>SUM(G2:G7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Потребитель</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pуст, кВт</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Сеть</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>П1В1: EC-вентиляторы, ротор, автоматика</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>380 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>П2: вентилятор, привод клапана, автоматика</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>230 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>В3: кухонный зонт</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>230 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>В2: вентилятор сауны</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>230 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ПУ1–ПУ6: паровые увлажнители</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>230/380 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Установка обратного осмоса (ВК)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>230 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>НБ1 (К1), Qх=20.0 кВт</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>380 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>НБ2 (К2), Qх=14.0 кВт</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>380 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ВБ1–ВБ11 канальные (вентиляторы)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>230 В</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Итого установленная</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>SUM(B2:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2314,7 +2752,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2361,11 +2799,11 @@
         <v/>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2412,11 +2850,11 @@
         <v/>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2467,7 +2905,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2518,7 +2956,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2569,7 +3007,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2616,11 +3054,11 @@
         <v/>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2671,7 +3109,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2722,7 +3160,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -2773,7 +3211,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2820,11 +3258,11 @@
         <v/>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>настенный</t>
+          <t>канальный</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2870,11 +3308,11 @@
         <v>20.04</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>22.4</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>ΣВБ=22.2 кВт, загрузка 99%</t>
+          <t>ΣВБ=19.8 кВт, загрузка 99%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
@@ -2901,11 +3339,11 @@
         <v>12.05</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>12.1</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>ΣВБ=15.0 кВт, загрузка 124%</t>
+          <t>ΣВБ=13.8 кВт, загрузка 99%</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -2915,13 +3353,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2984,12 +3422,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Приточно-вытяжная установка с роторным рекуператором (η≥75%), L=1050 м³/ч, Pсв=250 Па, EC-вентиляторы, электронагреватель 3.5 кВт / 380 В, фильтры приток ePM1 55% (F7), вытяжка ePM10 50% (M5), автоматика с пультом и датчиком CO₂</t>
+          <t>Приточно-вытяжная установка с роторным рекуператором (η≥80 %), L=1050/1050 м³/ч, Pсв=250 Па, EC-вентиляторы, водяной калорифер 7 кВт (гликоль 30 %, узел обвязки с насосом и 3-ходовым клапаном), фильтры приток ePM1 55 % (F7), вытяжка ePM10 50 % (M5), автоматика с Modbus TCP/RTU, датчиками CO₂/RH и защитой калорифера от замерзания</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Подвесная, для чердака, или аналог</t>
+          <t>Komfovent, Systemair или аналог</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3002,7 +3440,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Чердак, на виброопорах</t>
+          <t>Тёплый чердак над холлом, виброопоры</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3540,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Наружный воздух П1</t>
+          <t>К1 по БР-ЗК, ≥5 м от дымоходов</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3566,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Выброс В1</t>
+          <t>К2 по БР-ЗК, ≥3 м от забора</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3592,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2 этаж, по плану</t>
+          <t>2 этаж, от чердачных магистралей</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3604,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный/стеновой с пленумом под 2…4 воздуховода Ø90</t>
+          <t>Диффузор щелевой линейный 1–2 щели, L=1000 мм, с камерой статического давления и регулятором</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -3176,11 +3614,11 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1 этаж, по плану</t>
+          <t>1 этаж, приток у наружных стен</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3630,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Распределительный коллектор (камера статического давления) Ø200/Ø160, 6…14 выходов Ø90, со звукопоглощением и ревизией</t>
+          <t>Решётка/клапан вытяжной потолочный с регулятором Ø100…Ø160</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -3202,11 +3640,11 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>РК1–РК4: РК1=14, РК2=6, РК3=7, РК4=8 вых.</t>
+          <t>1 этаж, вытяжка</t>
         </is>
       </c>
     </row>
@@ -3218,21 +3656,21 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод полимерный гибкий двухслойный Ø90 с антистатическим и антибактериальным покрытием</t>
+          <t>Дроссель-клапан Ø125…Ø315 с ручным приводом</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21+14 линий × ≈12 м</t>
+          <t>Наладка</t>
         </is>
       </c>
     </row>
@@ -3244,21 +3682,21 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Дроссель-клапан Ø125…Ø315 с ручным приводом</t>
+          <t>Воздуховоды из оцинкованной стали круглые спирально-навивные, δ=0,5 мм, Ø100…Ø315 (ГОСТ 14918-2020)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Наладка</t>
+          <t>Чердак, шахты, подшивные потолки 1 эт.</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3708,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Воздуховоды из оцинкованной стали круглые спирально-навивные, δ=0,5 мм, Ø125…Ø315 (ГОСТ 14918-2020)</t>
+          <t>Фасонные изделия к воздуховодам п.10</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -3280,11 +3718,11 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ориентировочно</t>
+          <t>30% от п.10</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3734,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Фасонные изделия к воздуховодам п.11</t>
+          <t>Изоляция теплоизоляционная из вспененного каучука δ=19 мм, самоклеящаяся</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -3306,11 +3744,11 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30% от п.11</t>
+          <t>Приток после ПВУ в шахтах (от конденсации летом)</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3760,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Изоляция теплоизоляционная из вспененного каучука δ=19 мм, самоклеящаяся</t>
+          <t>Изоляция из вспененного каучука δ=32 мм, с покрытием (паронепроницаемая)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -3332,11 +3770,11 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Приток после ПВУ</t>
+          <t>Наружный воздух и выброс (тёплый чердак)</t>
         </is>
       </c>
     </row>
@@ -3348,21 +3786,21 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Изоляция из вспененного каучука δ=32 мм, с покрытием (паронепроницаемая)</t>
+          <t>Шланг дренажный ПВХ Ø20 с сифоном (гидрозатвор)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Наружный воздух, выброс</t>
+          <t>По паспорту ПВУ; чердак тёплый — без обогрева</t>
         </is>
       </c>
     </row>
@@ -3374,85 +3812,77 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Шланг дренажный ПВХ Ø20 с сифоном (гидрозатвор)</t>
+          <t>Датчик CO₂ + RH канальный/комнатный, выход 0–10 В или Modbus</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>При необходимости по паспорту ПВУ</t>
+          <t>Пом. 2-3, 2-7, 2-10, 2-12, 2-14, 1-9</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Система П2 / В3 (кухонный зонт и компенсация)</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Датчик перепада давления «помещение — улица» (дифманометр) с выходом в HA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Защита от опрокидывания тяги</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>П2</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Приточная установка компактная, L=400 м³/ч, Pсв=200 Па, электронагреватель 6 кВт / 380 В, фильтр G4, клапан с эл. приводом, автоматика с блокировкой от зонта</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Чердак</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Паровое увлажнение ПУ1–ПУ6</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>ПУ1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Вытяжной зонт кухонный с вентилятором, L=450 м³/ч</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -3460,25 +3890,25 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Поставка заказчика</t>
+          <t>Детская 10, 80 м³/ч, расч. 0.6 кг/ч</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>ПУ2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø200</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -3486,67 +3916,71 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>Детская 12, 80 м³/ч, расч. 0.6 кг/ч</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>ПУ3</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Воздуховоды из оцинкованной стали Ø200, δ=0,5 мм</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>П2, В3</t>
+          <t>Детская 14, 80 м³/ч, расч. 0.6 кг/ч</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>ПУ4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Изоляция вспененный каучук δ=32 мм с покрытием</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Гостевая 7, 80 м³/ч, расч. 0.6 кг/ч</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>ПУ5</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Узел прохода через кровлю Ø200 с зонтом</t>
+          <t>Пароувлажнитель канальный, 1.5 кг/ч, 1.12 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
@@ -3560,25 +3994,25 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>Мастер-спальня 3, 90 м³/ч, расч. 0.67 кг/ч</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>ПУ6</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная Ø200 с сеткой</t>
+          <t>Пароувлажнитель канальный, 3.0 кг/ч, 2.25 кВт, с паровой форсункой и гигростатом</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -3586,25 +4020,25 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>П2</t>
+          <t>Гостиная и кухня-столовая (через ВК-1), 370 м³/ч, расч. 2.75 кг/ч</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Решётка/диффузор приточный 400×150 с регулятором</t>
+          <t>Установка обратного осмоса 50–100 л/ч с баком 50 л (подпитка ПУ)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -3612,86 +4046,94 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Кухня, у зонта</t>
+          <t>Котельная, раздел ВК</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Система В2 (сауна)</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Трубопровод подпитки PE-X Ø16 и дренаж ПУ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Через ВК-5, дренаж в Ст.К1-4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>В2</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Вентилятор канальный термостойкий (до +120 °C), L=130 м³/ч, Pсв=150 Па, Ø125</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Работа в режиме просушки</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Система П2 / В3 (кухонный зонт и компенсация)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>П2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Клапан вытяжной для сауны регулируемый (дерево/нерж.) Ø125</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>Приточная установка компактная, L=400 м³/ч, Pсв=200 Па, водяной калорифер 5.5 кВт (гликоль 30 %), фильтр G4, утеплённый клапан с эл. приводом, шумоглушитель Ø200, автоматика с блокировкой от зонта</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Чердак, над ВК-2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø125</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>Вытяжной зонт кухонный с вентилятором, L=450 м³/ч, сухой контакт «вкл»</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>по дизайн-проекту</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3700,39 +4142,47 @@
       <c r="E31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Поставка заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод из нержавеющей стали Ø125, δ=0,5 мм</t>
+          <t>Клапан обратный Ø200 + клапан утеплённый Ø200 с эл. приводом</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>В3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Изоляция базальтовая фольгированная δ=30 мм</t>
+          <t>Воздуховоды из оцинкованной стали Ø200, δ=0,5 мм</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
@@ -3742,63 +4192,77 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>П2, В3</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Узел прохода через кровлю Ø125 с зонтом</t>
+          <t>Изоляция вспененный каучук δ=32 мм с покрытием</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Узел прохода через кровлю Ø200 с зонтом</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Системы ЕВ1, ПЕ1 (котельная), ПЕ2 (камин)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>В3 выброс, П2 забор</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Канал вытяжной естественный Ø200 оцинк. с утеплением δ=50 мм, с дефлектором над кровлей</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>ЕВ1</t>
-        </is>
-      </c>
+          <t>Решётка/диффузор приточный 400×150 с регулятором</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
@@ -3806,59 +4270,41 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Выше конька ≥0,5 м</t>
+          <t>Кухня, у зонта</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Решётка вентиляционная наружная 300×200 с утеплённой заслонкой</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>ПЕ1</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Нижняя зона котельной</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Система В2 (сауна)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод подачи воздуха на горение к топке камина Ø125 с заслонкой и наружной решёткой</t>
+          <t>Вентилятор канальный термостойкий (до +120 °C), L=130 м³/ч, Pсв=150 Па, Ø125</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ПЕ2</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
@@ -3866,38 +4312,44 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>По паспорту топки</t>
+          <t>Просушка по гигростату</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Системы кондиционирования К1, К2 (мини-VRF)</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Клапан вытяжной для сауны регулируемый (дерево/нерж.) Ø125</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>НБ1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRF (тепловой насос), Qх=22.4 кВт, R410A/R32, 380 В</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Клапан обратный Ø125</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3906,83 +4358,67 @@
       <c r="E40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Система К1, 99%</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>НБ2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRF (тепловой насос), Qх=12.1 кВт, R410A/R32, 380 В</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод из нержавеющей стали Ø125, δ=0,5 мм</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Система К2, 124%</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ВБ1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+          <t>Изоляция базальтовая фольгированная δ=30 мм</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1 эт., пом. 2</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ВБ2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=4.5 кВт</t>
+          <t>Узел прохода через кровлю Ø125 с зонтом</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
@@ -3990,19 +4426,19 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1 эт., пом. 7</t>
+          <t>К5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ВБ3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=7.1 кВт</t>
+          <t>Гигростат / датчик RH термостойкий для управления В2</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
@@ -4014,53 +4450,39 @@
       <c r="E44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1 эт., пом. 8</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>ВБ4</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Внутренний блок настенный, Qх=5.6 кВт</t>
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Системы ЕВ1, ПЕ1 (котельная), ПЕ2 (камин)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1 эт., пом. 9</t>
-        </is>
-      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ВБ5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>Канал вытяжной естественный Ø200 оцинк. с утеплением δ=50 мм, с дефлектором над кровлей</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ЕВ1</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
@@ -4068,22 +4490,26 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1 эт., пом. 12</t>
+          <t>В ВК-5, выше конька ≥0,5 м</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ВБ6</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>Решётка вентиляционная наружная 300×200 с утеплённой заслонкой и подогревом 300 Вт, воздуховод Ø160 через стену</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>ПЕ1</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -4094,25 +4520,29 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2 эт., пом. 3</t>
+          <t>П1 по БР-ЗК, нижняя зона котельной</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ВБ7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>Решётка 300×150 в наружной стене по оси 7 на уровне пола, с утеплённой заслонкой — воздух на горение камина</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>ПЕ2</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
@@ -4120,48 +4550,38 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2 эт., пом. 7</t>
+          <t>П3 по БР-ЗК</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ВБ8</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Системы кондиционирования К1, К2 (мульти-сплит / мини-VRF)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>2 эт., пом. 9</t>
-        </is>
-      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ВБ9</t>
+          <t>НБ1</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
+          <t>Наружный блок мульти-сплит / мини-VRF (тепловой насос), Qх=20.0 кВт, R32 или R410A, 380 В, шлюз Modbus</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -4172,22 +4592,26 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2 эт., пом. 10</t>
+          <t>Система К1, ΣВБ 19.8 кВт (99 %)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ВБ10</t>
+          <t>НБ2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.2 кВт</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
+          <t>Наружный блок мульти-сплит / мини-VRF (тепловой насос), Qх=14.0 кВт, R32 или R410A, 380 В, шлюз Modbus</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -4198,19 +4622,19 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2 эт., пом. 12</t>
+          <t>Система К2, ΣВБ 13.8 кВт (99 %)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ВБ11</t>
+          <t>ВБ1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок настенный, Qх=2.8 кВт</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
@@ -4224,159 +4648,175 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2 эт., пом. 14</t>
+          <t>1 эт., пом. 2 (расч. 1.3 кВт)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>ВБ2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель (рефнет) фреоновый</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>по ПО производителя</t>
-        </is>
-      </c>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=3.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1 эт., пом. 7 (расч. 4.05 кВт)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>ВБ3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая Ø6,35…Ø19,05 (ГОСТ Р 52318-2005)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=5.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Ориентировочно</t>
+          <t>1 эт., пом. 8 (расч. 6.66 кВт)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>ВБ4</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Изоляция трубная вспененный каучук δ=13 мм</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=5.6 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1 эт., пом. 9 (расч. 5.52 кВт)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>ВБ5</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Кабель межблочной связи экранированный 2×0,75</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.8 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1 эт., пом. 12 (расч. 2.51 кВт)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>ВБ6</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Дренажная труба ПП Ø32 с гидрозатвором (сухой затвор)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.8 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 3 (расч. 2.57 кВт)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>ВБ7</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Опора наружного блока (рама на фундаментных блоках)</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 7 (расч. 2.25 кВт)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>ВБ8</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления проводной индивидуальный</t>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
@@ -4386,9 +4826,261 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 9 (расч. 0.91 кВт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ВБ9</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 10 (расч. 2.06 кВт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ВБ10</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 12 (расч. 2.06 кВт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ВБ11</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний блок канальный скрытого монтажа, Qх=2.2 кВт, Pсв ≥ 30 Па, с решётками притока/возврата</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2 эт., пом. 14 (расч. 2.2 кВт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Разветвитель (рефнет) фреоновый</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>по ПО производителя</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Труба медная отожжённая Ø6,35…Ø19,05 (ГОСТ Р 52318-2005)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Ориентировочно</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Изоляция трубная вспененный каучук δ=13 мм</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Кабель межблочной связи экранированный 2×0,75</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Дренажная труба ПП Ø32 с гидрозатвором (сухой затвор), дренажные помпы где нет уклона</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Помпы ≈ 4 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Короб декоративный с жалюзи для НБ1, НБ2 на опорах h ≥ 400 мм</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>У южной стены котельной, ось Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Шлюз Modbus/BACnet для внутренних блоков (интеграция в Home Assistant)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
